--- a/salidas/empresas/PRU.xlsx
+++ b/salidas/empresas/PRU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>36.64836120605469</v>
+        <v>36.64837265014648</v>
       </c>
       <c r="C2" t="n">
         <v>75.33999633789062</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>37.47531509399414</v>
+        <v>37.47530364990234</v>
       </c>
       <c r="C3" t="n">
         <v>77.04000091552734</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>36.87700653076172</v>
+        <v>36.87701034545898</v>
       </c>
       <c r="C4" t="n">
         <v>75.80999755859375</v>
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>37.04238891601562</v>
+        <v>37.04239273071289</v>
       </c>
       <c r="C6" t="n">
         <v>76.15000152587891</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>37.79636001586914</v>
+        <v>37.79635620117188</v>
       </c>
       <c r="C7" t="n">
         <v>77.69999694824219</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>38.25363159179688</v>
+        <v>38.25362396240234</v>
       </c>
       <c r="C8" t="n">
         <v>78.63999938964844</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>35.70955657958984</v>
+        <v>35.70955276489258</v>
       </c>
       <c r="C9" t="n">
         <v>73.41000366210938</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>37.09102630615234</v>
+        <v>37.09103393554688</v>
       </c>
       <c r="C10" t="n">
         <v>76.25</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>37.42180633544922</v>
+        <v>37.42182159423828</v>
       </c>
       <c r="C11" t="n">
         <v>76.93000030517578</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>40.10715103149414</v>
+        <v>40.10713195800781</v>
       </c>
       <c r="C12" t="n">
         <v>81.48000335693359</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>42.26313018798828</v>
+        <v>42.26313400268555</v>
       </c>
       <c r="C13" t="n">
         <v>85.86000061035156</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>43.87271499633789</v>
+        <v>43.87273025512695</v>
       </c>
       <c r="C14" t="n">
         <v>89.12999725341797</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>44.76366806030273</v>
+        <v>44.763671875</v>
       </c>
       <c r="C15" t="n">
         <v>90.94000244140625</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>44.42893981933594</v>
+        <v>44.42894744873047</v>
       </c>
       <c r="C16" t="n">
         <v>90.26000213623047</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>46.76211166381836</v>
+        <v>46.76213455200195</v>
       </c>
       <c r="C17" t="n">
         <v>95</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>50.21760177612305</v>
+        <v>50.21760559082031</v>
       </c>
       <c r="C18" t="n">
         <v>102.0199966430664</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>47.85982131958008</v>
+        <v>47.85981369018555</v>
       </c>
       <c r="C19" t="n">
         <v>97.23000335693359</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>43.62659454345703</v>
+        <v>43.62660980224609</v>
       </c>
       <c r="C20" t="n">
         <v>88.62999725341797</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>44.19267272949219</v>
+        <v>44.19267654418945</v>
       </c>
       <c r="C21" t="n">
         <v>89.77999877929688</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>48.03208160400391</v>
+        <v>48.03208923339844</v>
       </c>
       <c r="C22" t="n">
         <v>97.58000183105469</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>47.6087646484375</v>
+        <v>47.60878753662109</v>
       </c>
       <c r="C23" t="n">
         <v>96.72000122070312</v>
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>46.35704040527344</v>
+        <v>46.35703277587891</v>
       </c>
       <c r="C25" t="n">
         <v>93.04000091552734</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>41.88776397705078</v>
+        <v>41.88776779174805</v>
       </c>
       <c r="C26" t="n">
         <v>84.06999969482422</v>
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>38.98795700073242</v>
+        <v>38.98794555664062</v>
       </c>
       <c r="C28" t="n">
         <v>78.25</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>37.72240447998047</v>
+        <v>37.72239303588867</v>
       </c>
       <c r="C29" t="n">
         <v>75.70999908447266</v>
@@ -1014,7 +1026,7 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>29.76536560058594</v>
+        <v>29.76537895202637</v>
       </c>
       <c r="C31" t="n">
         <v>59.7400016784668</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>34.36420059204102</v>
+        <v>34.36419677734375</v>
       </c>
       <c r="C32" t="n">
         <v>68.97000122070312</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>36.72590637207031</v>
+        <v>36.72590255737305</v>
       </c>
       <c r="C33" t="n">
         <v>73.70999908447266</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>35.8739013671875</v>
+        <v>35.87389755249023</v>
       </c>
       <c r="C34" t="n">
         <v>72</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>14.94745635986328</v>
+        <v>14.9474515914917</v>
       </c>
       <c r="C35" t="n">
         <v>30</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>11.19367218017578</v>
+        <v>11.1936674118042</v>
       </c>
       <c r="C36" t="n">
         <v>21.70000076293945</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>15.60924053192139</v>
+        <v>15.60923957824707</v>
       </c>
       <c r="C37" t="n">
         <v>30.26000022888184</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>13.28281021118164</v>
+        <v>13.28280925750732</v>
       </c>
       <c r="C38" t="n">
         <v>25.75</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>8.464888572692871</v>
+        <v>8.464890480041504</v>
       </c>
       <c r="C39" t="n">
         <v>16.40999984741211</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>9.811226844787598</v>
+        <v>9.811227798461914</v>
       </c>
       <c r="C40" t="n">
         <v>19.02000045776367</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>14.89737796783447</v>
+        <v>14.89738464355469</v>
       </c>
       <c r="C41" t="n">
         <v>28.8799991607666</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>20.58707046508789</v>
+        <v>20.58706855773926</v>
       </c>
       <c r="C42" t="n">
         <v>39.90999984741211</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>19.199462890625</v>
+        <v>19.19947242736816</v>
       </c>
       <c r="C43" t="n">
         <v>37.22000122070312</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>22.83612060546875</v>
+        <v>22.83612251281738</v>
       </c>
       <c r="C44" t="n">
         <v>44.27000045776367</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>26.09106254577637</v>
+        <v>26.09104919433594</v>
       </c>
       <c r="C45" t="n">
         <v>50.58000183105469</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>25.74544334411621</v>
+        <v>25.74543571472168</v>
       </c>
       <c r="C46" t="n">
         <v>49.90999984741211</v>
@@ -1349,7 +1361,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>26.08973693847656</v>
+        <v>26.0897159576416</v>
       </c>
       <c r="C48" t="n">
         <v>49.84999847412109</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>26.04262924194336</v>
+        <v>26.04262542724609</v>
       </c>
       <c r="C49" t="n">
         <v>49.7599983215332</v>
@@ -1424,7 +1436,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
@@ -1449,7 +1461,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>31.6635570526123</v>
+        <v>31.66356658935547</v>
       </c>
       <c r="C52" t="n">
         <v>60.5</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>33.26506042480469</v>
+        <v>33.26506423950195</v>
       </c>
       <c r="C53" t="n">
         <v>63.56000137329102</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>30.20337295532227</v>
+        <v>30.20337867736816</v>
       </c>
       <c r="C54" t="n">
         <v>57.70999908447266</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>28.08373832702637</v>
+        <v>28.08374786376953</v>
       </c>
       <c r="C55" t="n">
         <v>53.65999984741211</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>29.98355865478516</v>
+        <v>29.98356628417969</v>
       </c>
       <c r="C56" t="n">
         <v>57.29000091552734</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>26.48224639892578</v>
+        <v>26.48226356506348</v>
       </c>
       <c r="C57" t="n">
         <v>50.59999847412109</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>28.35589599609375</v>
+        <v>28.35589981079102</v>
       </c>
       <c r="C58" t="n">
         <v>54.18000030517578</v>
@@ -1649,7 +1661,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
@@ -1668,11 +1680,11 @@
       <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>27.09620094299316</v>
+        <v>27.09619522094727</v>
       </c>
       <c r="C60" t="n">
         <v>50.68000030517578</v>
@@ -1687,11 +1699,11 @@
       <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>31.38945007324219</v>
+        <v>31.38945770263672</v>
       </c>
       <c r="C61" t="n">
         <v>58.70999908447266</v>
@@ -1706,11 +1718,11 @@
       <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>32.886474609375</v>
+        <v>32.88647842407227</v>
       </c>
       <c r="C62" t="n">
         <v>61.5099983215332</v>
@@ -1725,11 +1737,11 @@
       <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>35.19618225097656</v>
+        <v>35.1961784362793</v>
       </c>
       <c r="C63" t="n">
         <v>65.83000183105469</v>
@@ -1748,11 +1760,11 @@
       <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>32.92389678955078</v>
+        <v>32.92390060424805</v>
       </c>
       <c r="C64" t="n">
         <v>61.58000183105469</v>
@@ -1771,11 +1783,11 @@
       <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>33.90767288208008</v>
+        <v>33.90766906738281</v>
       </c>
       <c r="C65" t="n">
         <v>63.41999816894531</v>
@@ -1794,11 +1806,11 @@
       <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>34.10013580322266</v>
+        <v>34.10013961791992</v>
       </c>
       <c r="C66" t="n">
         <v>63.77999877929688</v>
@@ -1817,11 +1829,11 @@
       <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>33.99856185913086</v>
+        <v>33.9985466003418</v>
       </c>
       <c r="C67" t="n">
         <v>63.59000015258789</v>
@@ -1840,7 +1852,7 @@
       <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
@@ -1863,11 +1875,11 @@
       <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>26.84490013122559</v>
+        <v>26.84491157531738</v>
       </c>
       <c r="C69" t="n">
         <v>50.20999908447266</v>
@@ -1886,11 +1898,11 @@
       <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>25.0538215637207</v>
+        <v>25.05383110046387</v>
       </c>
       <c r="C70" t="n">
         <v>46.86000061035156</v>
@@ -1909,11 +1921,11 @@
       <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>28.97818183898926</v>
+        <v>28.97816848754883</v>
       </c>
       <c r="C71" t="n">
         <v>54.20000076293945</v>
@@ -1928,11 +1940,11 @@
       <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>27.87534713745117</v>
+        <v>27.8753490447998</v>
       </c>
       <c r="C72" t="n">
         <v>50.63999938964844</v>
@@ -1947,11 +1959,11 @@
       <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>27.58909606933594</v>
+        <v>27.58909797668457</v>
       </c>
       <c r="C73" t="n">
         <v>50.11999893188477</v>
@@ -1966,11 +1978,11 @@
       <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>31.50838279724121</v>
+        <v>31.50839233398438</v>
       </c>
       <c r="C74" t="n">
         <v>57.2400016784668</v>
@@ -1985,7 +1997,7 @@
       <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2008,11 +2020,11 @@
       <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>34.89372253417969</v>
+        <v>34.89371109008789</v>
       </c>
       <c r="C76" t="n">
         <v>63.38999938964844</v>
@@ -2031,7 +2043,7 @@
       <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2054,11 +2066,11 @@
       <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>25.56892204284668</v>
+        <v>25.56891441345215</v>
       </c>
       <c r="C78" t="n">
         <v>46.45000076293945</v>
@@ -2077,11 +2089,11 @@
       <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>26.65882110595703</v>
+        <v>26.65882873535156</v>
       </c>
       <c r="C79" t="n">
         <v>48.43000030517578</v>
@@ -2100,11 +2112,11 @@
       <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>26.57625961303711</v>
+        <v>26.57625198364258</v>
       </c>
       <c r="C80" t="n">
         <v>48.27999877929688</v>
@@ -2123,11 +2135,11 @@
       <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>30.00563430786133</v>
+        <v>30.00562477111816</v>
       </c>
       <c r="C81" t="n">
         <v>54.5099983215332</v>
@@ -2146,11 +2158,11 @@
       <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>30.00563430786133</v>
+        <v>30.00562477111816</v>
       </c>
       <c r="C82" t="n">
         <v>54.5099983215332</v>
@@ -2169,11 +2181,11 @@
       <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>31.40380668640137</v>
+        <v>31.40380477905273</v>
       </c>
       <c r="C83" t="n">
         <v>57.04999923706055</v>
@@ -2192,7 +2204,7 @@
       <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2215,11 +2227,11 @@
       <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>30.31817626953125</v>
+        <v>30.31818962097168</v>
       </c>
       <c r="C85" t="n">
         <v>53.33000183105469</v>
@@ -2234,11 +2246,11 @@
       <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>32.90486907958984</v>
+        <v>32.90487289428711</v>
       </c>
       <c r="C86" t="n">
         <v>57.88000106811523</v>
@@ -2253,11 +2265,11 @@
       <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>31.82259559631348</v>
+        <v>31.82259750366211</v>
       </c>
       <c r="C87" t="n">
         <v>55.56999969482422</v>
@@ -2276,7 +2288,7 @@
       <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
@@ -2299,11 +2311,11 @@
       <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>34.59999084472656</v>
+        <v>34.59999847412109</v>
       </c>
       <c r="C89" t="n">
         <v>60.41999816894531</v>
@@ -2322,11 +2334,11 @@
       <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>39.73347091674805</v>
+        <v>39.73347473144531</v>
       </c>
       <c r="C90" t="n">
         <v>68.97000122070312</v>
@@ -2351,11 +2363,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>42.07242584228516</v>
+        <v>42.07242965698242</v>
       </c>
       <c r="C91" t="n">
         <v>73.02999877929688</v>
@@ -2380,11 +2392,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>45.49444961547852</v>
+        <v>45.49445343017578</v>
       </c>
       <c r="C92" t="n">
         <v>78.97000122070312</v>
@@ -2409,11 +2421,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>43.3563346862793</v>
+        <v>43.35632705688477</v>
       </c>
       <c r="C93" t="n">
         <v>74.87999725341797</v>
@@ -2438,11 +2450,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>45.15126419067383</v>
+        <v>45.15127563476562</v>
       </c>
       <c r="C94" t="n">
         <v>77.98000335693359</v>
@@ -2467,11 +2479,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>47.12569808959961</v>
+        <v>47.12568283081055</v>
       </c>
       <c r="C95" t="n">
         <v>81.38999938964844</v>
@@ -2496,11 +2508,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>51.69676208496094</v>
+        <v>51.6967658996582</v>
       </c>
       <c r="C96" t="n">
         <v>88.76000213623047</v>
@@ -2525,7 +2537,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2550,11 +2562,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>49.15151977539062</v>
+        <v>49.15151596069336</v>
       </c>
       <c r="C98" t="n">
         <v>84.38999938964844</v>
@@ -2575,7 +2587,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2602,11 +2614,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>49.61417770385742</v>
+        <v>49.61418151855469</v>
       </c>
       <c r="C100" t="n">
         <v>84.65000152587891</v>
@@ -2629,11 +2641,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>47.28732299804688</v>
+        <v>47.28731918334961</v>
       </c>
       <c r="C101" t="n">
         <v>80.68000030517578</v>
@@ -2656,7 +2668,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2685,11 +2697,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>52.37125396728516</v>
+        <v>52.37125015258789</v>
       </c>
       <c r="C103" t="n">
         <v>88.76999664306641</v>
@@ -2714,11 +2726,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>51.30930709838867</v>
+        <v>51.30931091308594</v>
       </c>
       <c r="C104" t="n">
         <v>86.97000122070312</v>
@@ -2743,11 +2755,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>53.23299407958984</v>
+        <v>53.23298263549805</v>
       </c>
       <c r="C105" t="n">
         <v>89.69999694824219</v>
@@ -2772,11 +2784,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>52.18848419189453</v>
+        <v>52.18850326538086</v>
       </c>
       <c r="C106" t="n">
         <v>87.94000244140625</v>
@@ -2801,7 +2813,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
@@ -2830,7 +2842,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -2859,11 +2871,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>54.05703353881836</v>
+        <v>54.0570182800293</v>
       </c>
       <c r="C109" t="n">
         <v>90.45999908447266</v>
@@ -2884,11 +2896,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>45.34432220458984</v>
+        <v>45.34434127807617</v>
       </c>
       <c r="C110" t="n">
         <v>75.87999725341797</v>
@@ -2909,11 +2921,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>48.66581726074219</v>
+        <v>48.66580581665039</v>
       </c>
       <c r="C111" t="n">
         <v>80.84999847412109</v>
@@ -2938,11 +2950,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>48.34076690673828</v>
+        <v>48.34075546264648</v>
       </c>
       <c r="C112" t="n">
         <v>80.30999755859375</v>
@@ -2967,11 +2979,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>49.11724853515625</v>
+        <v>49.11725616455078</v>
       </c>
       <c r="C113" t="n">
         <v>81.59999847412109</v>
@@ -2996,11 +3008,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>51.27632904052734</v>
+        <v>51.27630996704102</v>
       </c>
       <c r="C114" t="n">
         <v>84.61000061035156</v>
@@ -3025,11 +3037,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>53.03989791870117</v>
+        <v>53.03987884521484</v>
       </c>
       <c r="C115" t="n">
         <v>87.51999664306641</v>
@@ -3054,7 +3066,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -3083,11 +3095,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>49.24319839477539</v>
+        <v>49.2431755065918</v>
       </c>
       <c r="C117" t="n">
         <v>80.69999694824219</v>
@@ -3112,11 +3124,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>46.50338745117188</v>
+        <v>46.50337982177734</v>
       </c>
       <c r="C118" t="n">
         <v>76.20999908447266</v>
@@ -3141,11 +3153,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>50.341552734375</v>
+        <v>50.3415412902832</v>
       </c>
       <c r="C119" t="n">
         <v>82.5</v>
@@ -3170,11 +3182,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>53.23927307128906</v>
+        <v>53.2392578125</v>
       </c>
       <c r="C120" t="n">
         <v>86.55000305175781</v>
@@ -3199,11 +3211,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>50.07752227783203</v>
+        <v>50.07751846313477</v>
       </c>
       <c r="C121" t="n">
         <v>81.41000366210938</v>
@@ -3228,7 +3240,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3257,11 +3269,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>41.088623046875</v>
+        <v>41.08862686157227</v>
       </c>
       <c r="C123" t="n">
         <v>66.08999633789062</v>
@@ -3286,11 +3298,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>44.89970016479492</v>
+        <v>44.89968872070312</v>
       </c>
       <c r="C124" t="n">
         <v>72.22000122070312</v>
@@ -3315,11 +3327,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>48.26935958862305</v>
+        <v>48.26936340332031</v>
       </c>
       <c r="C125" t="n">
         <v>77.63999938964844</v>
@@ -3344,11 +3356,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>49.71761322021484</v>
+        <v>49.71763229370117</v>
       </c>
       <c r="C126" t="n">
         <v>79.25</v>
@@ -3373,11 +3385,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>44.75526428222656</v>
+        <v>44.75527572631836</v>
       </c>
       <c r="C127" t="n">
         <v>71.33999633789062</v>
@@ -3402,7 +3414,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3431,11 +3443,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>50.25895309448242</v>
+        <v>50.25894165039062</v>
       </c>
       <c r="C129" t="n">
         <v>79.37999725341797</v>
@@ -3460,11 +3472,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>51.69618225097656</v>
+        <v>51.6961669921875</v>
       </c>
       <c r="C130" t="n">
         <v>81.65000152587891</v>
@@ -3489,7 +3501,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -3518,11 +3530,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>64.14708709716797</v>
+        <v>64.1470947265625</v>
       </c>
       <c r="C132" t="n">
         <v>100.5999984741211</v>
@@ -3547,11 +3559,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>66.35334014892578</v>
+        <v>66.35330963134766</v>
       </c>
       <c r="C133" t="n">
         <v>104.0599975585938</v>
@@ -3576,11 +3588,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>67.02288055419922</v>
+        <v>67.02287292480469</v>
       </c>
       <c r="C134" t="n">
         <v>105.1100006103516</v>
@@ -3605,11 +3617,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>70.95997619628906</v>
+        <v>70.95999145507812</v>
       </c>
       <c r="C135" t="n">
         <v>110.5400009155273</v>
@@ -3634,11 +3646,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>68.48213958740234</v>
+        <v>68.48209381103516</v>
       </c>
       <c r="C136" t="n">
         <v>106.6800003051758</v>
@@ -3663,11 +3675,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>68.70677185058594</v>
+        <v>68.70680236816406</v>
       </c>
       <c r="C137" t="n">
         <v>107.0299987792969</v>
@@ -3692,11 +3704,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>67.79888153076172</v>
+        <v>67.79888916015625</v>
       </c>
       <c r="C138" t="n">
         <v>104.8499984741211</v>
@@ -3721,11 +3733,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>69.92630004882812</v>
+        <v>69.92627716064453</v>
       </c>
       <c r="C139" t="n">
         <v>108.1399993896484</v>
@@ -3750,11 +3762,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>73.21762084960938</v>
+        <v>73.2176513671875</v>
       </c>
       <c r="C140" t="n">
         <v>113.2300033569336</v>
@@ -3779,11 +3791,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>66.49352264404297</v>
+        <v>66.49349212646484</v>
       </c>
       <c r="C141" t="n">
         <v>102.0800018310547</v>
@@ -3808,11 +3820,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>69.25539398193359</v>
+        <v>69.25537872314453</v>
       </c>
       <c r="C142" t="n">
         <v>106.3199996948242</v>
@@ -3837,11 +3849,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>71.95212554931641</v>
+        <v>71.9521484375</v>
       </c>
       <c r="C143" t="n">
         <v>110.4599990844727</v>
@@ -3866,11 +3878,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>75.97603607177734</v>
+        <v>75.97600555419922</v>
       </c>
       <c r="C144" t="n">
         <v>115.8399963378906</v>
@@ -3895,11 +3907,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>75.41200256347656</v>
+        <v>75.41199493408203</v>
       </c>
       <c r="C145" t="n">
         <v>114.9800033569336</v>
@@ -3924,11 +3936,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>77.93051910400391</v>
+        <v>77.93051147460938</v>
       </c>
       <c r="C146" t="n">
         <v>118.8199996948242</v>
@@ -3953,11 +3965,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>70.31040954589844</v>
+        <v>70.31039428710938</v>
       </c>
       <c r="C147" t="n">
         <v>106.3199996948242</v>
@@ -3982,7 +3994,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4011,11 +4023,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>70.31040954589844</v>
+        <v>70.31039428710938</v>
       </c>
       <c r="C149" t="n">
         <v>106.3199996948242</v>
@@ -4040,11 +4052,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>64.60887908935547</v>
+        <v>64.60887145996094</v>
       </c>
       <c r="C150" t="n">
         <v>96.83999633789062</v>
@@ -4069,11 +4081,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>62.38718795776367</v>
+        <v>62.38719177246094</v>
       </c>
       <c r="C151" t="n">
         <v>93.51000213623047</v>
@@ -4098,11 +4110,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>67.32427215576172</v>
+        <v>67.32426452636719</v>
       </c>
       <c r="C152" t="n">
         <v>100.9100036621094</v>
@@ -4127,11 +4139,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>66.15219116210938</v>
+        <v>66.15218353271484</v>
       </c>
       <c r="C153" t="n">
         <v>98.25</v>
@@ -4156,11 +4168,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>68.21924591064453</v>
+        <v>68.21925354003906</v>
       </c>
       <c r="C154" t="n">
         <v>101.3199996948242</v>
@@ -4185,11 +4197,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>63.14252853393555</v>
+        <v>63.14250564575195</v>
       </c>
       <c r="C155" t="n">
         <v>93.77999877929688</v>
@@ -4214,11 +4226,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>63.75936889648438</v>
+        <v>63.75935745239258</v>
       </c>
       <c r="C156" t="n">
         <v>93.76000213623047</v>
@@ -4243,11 +4255,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>55.45622253417969</v>
+        <v>55.45622634887695</v>
       </c>
       <c r="C157" t="n">
         <v>81.55000305175781</v>
@@ -4272,11 +4284,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>62.65771484375</v>
+        <v>62.65769577026367</v>
       </c>
       <c r="C158" t="n">
         <v>92.13999938964844</v>
@@ -4301,11 +4313,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>65.88035583496094</v>
+        <v>65.88037109375</v>
       </c>
       <c r="C159" t="n">
         <v>95.84999847412109</v>
@@ -4330,11 +4342,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>63.15166854858398</v>
+        <v>63.15167236328125</v>
       </c>
       <c r="C160" t="n">
         <v>91.87999725341797</v>
@@ -4359,11 +4371,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>72.65741729736328</v>
+        <v>72.65739440917969</v>
       </c>
       <c r="C161" t="n">
         <v>105.7099990844727</v>
@@ -4388,11 +4400,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>64.15599822998047</v>
+        <v>64.15599060058594</v>
       </c>
       <c r="C162" t="n">
         <v>92.37999725341797</v>
@@ -4417,11 +4429,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>70.14239501953125</v>
+        <v>70.14240264892578</v>
       </c>
       <c r="C163" t="n">
         <v>101</v>
@@ -4446,11 +4458,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>70.35768890380859</v>
+        <v>70.357666015625</v>
       </c>
       <c r="C164" t="n">
         <v>101.3099975585938</v>
@@ -4475,11 +4487,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>56.30725860595703</v>
+        <v>56.3072509765625</v>
       </c>
       <c r="C165" t="n">
         <v>80.08999633789062</v>
@@ -4504,11 +4516,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>63.23932266235352</v>
+        <v>63.23933410644531</v>
       </c>
       <c r="C166" t="n">
         <v>89.94999694824219</v>
@@ -4533,7 +4545,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4562,7 +4574,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4591,11 +4603,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>66.60543823242188</v>
+        <v>66.60544586181641</v>
       </c>
       <c r="C169" t="n">
         <v>93.73999786376953</v>
@@ -4620,11 +4632,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>64.70121002197266</v>
+        <v>64.70120239257812</v>
       </c>
       <c r="C170" t="n">
         <v>91.05999755859375</v>
@@ -4649,11 +4661,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>54.23400115966797</v>
+        <v>54.23398590087891</v>
       </c>
       <c r="C171" t="n">
         <v>75.44999694824219</v>
@@ -4678,11 +4690,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>37.47859954833984</v>
+        <v>37.47861099243164</v>
       </c>
       <c r="C172" t="n">
         <v>52.13999938964844</v>
@@ -4707,11 +4719,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>44.83200836181641</v>
+        <v>44.83200454711914</v>
       </c>
       <c r="C173" t="n">
         <v>62.36999893188477</v>
@@ -4736,11 +4748,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>44.67052841186523</v>
+        <v>44.6705436706543</v>
       </c>
       <c r="C174" t="n">
         <v>60.95999908447266</v>
@@ -4765,7 +4777,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -4794,11 +4806,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>46.43653869628906</v>
+        <v>46.43654632568359</v>
       </c>
       <c r="C176" t="n">
         <v>63.36999893188477</v>
@@ -4823,11 +4835,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>50.48460388183594</v>
+        <v>50.48459625244141</v>
       </c>
       <c r="C177" t="n">
         <v>67.76999664306641</v>
@@ -4850,11 +4862,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>47.31861114501953</v>
+        <v>47.31860733032227</v>
       </c>
       <c r="C178" t="n">
         <v>63.52000045776367</v>
@@ -4877,11 +4889,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>47.69108200073242</v>
+        <v>47.69108581542969</v>
       </c>
       <c r="C179" t="n">
         <v>64.01999664306641</v>
@@ -4904,7 +4916,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -4931,11 +4943,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>59.01560974121094</v>
+        <v>59.015625</v>
       </c>
       <c r="C181" t="n">
         <v>78.06999969482422</v>
@@ -4958,11 +4970,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>59.17436981201172</v>
+        <v>59.17435073852539</v>
       </c>
       <c r="C182" t="n">
         <v>78.27999877929688</v>
@@ -4985,11 +4997,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>66.49468994140625</v>
+        <v>66.49467468261719</v>
       </c>
       <c r="C183" t="n">
         <v>86.72000122070312</v>
@@ -5012,11 +5024,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>69.85312652587891</v>
+        <v>69.8531494140625</v>
       </c>
       <c r="C184" t="n">
         <v>91.09999847412109</v>
@@ -5039,7 +5051,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5066,7 +5078,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5095,11 +5107,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>79.42579650878906</v>
+        <v>79.42581939697266</v>
       </c>
       <c r="C187" t="n">
         <v>102.4700012207031</v>
@@ -5124,11 +5136,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>77.72830963134766</v>
+        <v>77.72831726074219</v>
       </c>
       <c r="C188" t="n">
         <v>100.2799987792969</v>
@@ -5153,11 +5165,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>82.98354339599609</v>
+        <v>82.98356628417969</v>
       </c>
       <c r="C189" t="n">
         <v>105.879997253418</v>
@@ -5182,11 +5194,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>82.45061492919922</v>
+        <v>82.45059204101562</v>
       </c>
       <c r="C190" t="n">
         <v>105.1999969482422</v>
@@ -5211,11 +5223,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>86.25179290771484</v>
+        <v>86.25180053710938</v>
       </c>
       <c r="C191" t="n">
         <v>110.0500030517578</v>
@@ -5240,11 +5252,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>81.02099609375</v>
+        <v>81.02101135253906</v>
       </c>
       <c r="C192" t="n">
         <v>102.2600021362305</v>
@@ -5269,11 +5281,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>85.75898742675781</v>
+        <v>85.75897216796875</v>
       </c>
       <c r="C193" t="n">
         <v>108.2399978637695</v>
@@ -5298,11 +5310,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>88.39735412597656</v>
+        <v>88.3973388671875</v>
       </c>
       <c r="C194" t="n">
         <v>111.5699996948242</v>
@@ -5327,11 +5339,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>89.36334228515625</v>
+        <v>89.36333465576172</v>
       </c>
       <c r="C195" t="n">
         <v>111.6600036621094</v>
@@ -5356,11 +5368,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>94.57338714599609</v>
+        <v>94.57340240478516</v>
       </c>
       <c r="C196" t="n">
         <v>118.1699981689453</v>
@@ -5385,11 +5397,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>86.84233856201172</v>
+        <v>86.84233093261719</v>
       </c>
       <c r="C197" t="n">
         <v>108.5100021362305</v>
@@ -5414,11 +5426,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>86.08019256591797</v>
+        <v>86.08017730712891</v>
       </c>
       <c r="C198" t="n">
         <v>106.25</v>
@@ -5443,11 +5455,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>77.51673889160156</v>
+        <v>77.51673126220703</v>
       </c>
       <c r="C199" t="n">
         <v>95.68000030517578</v>
@@ -5472,11 +5484,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>81.00855255126953</v>
+        <v>81.008544921875</v>
       </c>
       <c r="C200" t="n">
         <v>99.98999786376953</v>
@@ -5501,11 +5513,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>78.48429107666016</v>
+        <v>78.48427581787109</v>
       </c>
       <c r="C201" t="n">
         <v>95.75</v>
@@ -5530,11 +5542,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>70.31208801269531</v>
+        <v>70.31209564208984</v>
       </c>
       <c r="C202" t="n">
         <v>85.77999877929688</v>
@@ -5559,11 +5571,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>86.22206115722656</v>
+        <v>86.22206878662109</v>
       </c>
       <c r="C203" t="n">
         <v>105.1900024414062</v>
@@ -5588,7 +5600,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5617,11 +5629,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>82.44709014892578</v>
+        <v>82.44709777832031</v>
       </c>
       <c r="C205" t="n">
         <v>99.45999908447266</v>
@@ -5646,7 +5658,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5675,11 +5687,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>83.9119873046875</v>
+        <v>83.91197967529297</v>
       </c>
       <c r="C207" t="n">
         <v>100</v>
@@ -5702,11 +5714,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>69.42879486083984</v>
+        <v>69.42877197265625</v>
       </c>
       <c r="C208" t="n">
         <v>82.73999786376953</v>
@@ -5729,7 +5741,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -5756,11 +5768,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>67.05197143554688</v>
+        <v>67.05197906494141</v>
       </c>
       <c r="C210" t="n">
         <v>78.69000244140625</v>
@@ -5785,7 +5797,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -5814,11 +5826,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>82.21942138671875</v>
+        <v>82.21941375732422</v>
       </c>
       <c r="C212" t="n">
         <v>96.48999786376953</v>
@@ -5843,7 +5855,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -5872,7 +5884,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -5901,11 +5913,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>78.98014068603516</v>
+        <v>78.98013305664062</v>
       </c>
       <c r="C215" t="n">
         <v>91.44000244140625</v>
@@ -5930,11 +5942,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>85.57339477539062</v>
+        <v>85.57337951660156</v>
       </c>
       <c r="C216" t="n">
         <v>97.77999877929688</v>
@@ -5959,11 +5971,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>90.76308441162109</v>
+        <v>90.76309967041016</v>
       </c>
       <c r="C217" t="n">
         <v>103.7099990844727</v>
@@ -5988,7 +6000,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6017,7 +6029,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6046,11 +6058,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>103.9809188842773</v>
+        <v>103.9809265136719</v>
       </c>
       <c r="C220" t="n">
         <v>117.4000015258789</v>
@@ -6075,7 +6087,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6104,7 +6116,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6133,11 +6145,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>104.9192810058594</v>
+        <v>104.9192886352539</v>
       </c>
       <c r="C223" t="n">
         <v>117.1900024414062</v>
@@ -6162,11 +6174,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>112.1979904174805</v>
+        <v>112.1980056762695</v>
       </c>
       <c r="C224" t="n">
         <v>125.3199996948242</v>
@@ -6191,7 +6203,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6220,11 +6232,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>109.6511535644531</v>
+        <v>109.6511383056641</v>
       </c>
       <c r="C226" t="n">
         <v>121.0999984741211</v>
@@ -6249,7 +6261,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6278,11 +6290,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>118.3764724731445</v>
+        <v>118.3764801025391</v>
       </c>
       <c r="C228" t="n">
         <v>129.4100036621094</v>
@@ -6307,11 +6319,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>108.4240951538086</v>
+        <v>108.4241027832031</v>
       </c>
       <c r="C229" t="n">
         <v>118.5299987792969</v>
@@ -6336,11 +6348,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>110.4639739990234</v>
+        <v>110.4639663696289</v>
       </c>
       <c r="C230" t="n">
         <v>120.7600021362305</v>
@@ -6365,11 +6377,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>106.5762329101562</v>
+        <v>106.5762252807617</v>
       </c>
       <c r="C231" t="n">
         <v>115.0999984741211</v>
@@ -6394,7 +6406,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6423,7 +6435,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6452,11 +6464,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>97.41429138183594</v>
+        <v>97.41429901123047</v>
       </c>
       <c r="C234" t="n">
         <v>103.8899993896484</v>
@@ -6481,11 +6493,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>100.7430267333984</v>
+        <v>100.7430191040039</v>
       </c>
       <c r="C235" t="n">
         <v>107.4400024414062</v>
@@ -6510,7 +6522,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6539,7 +6551,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6568,7 +6580,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6597,7 +6609,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6626,11 +6638,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>104.162727355957</v>
+        <v>104.1627197265625</v>
       </c>
       <c r="C240" t="n">
         <v>108.25</v>
@@ -6655,11 +6667,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>108.6179046630859</v>
+        <v>108.6178970336914</v>
       </c>
       <c r="C241" t="n">
         <v>112.879997253418</v>
@@ -6684,11 +6696,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>106.9147491455078</v>
+        <v>106.9147415161133</v>
       </c>
       <c r="C242" t="n">
         <v>111.1100006103516</v>
@@ -6713,7 +6725,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6742,7 +6754,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6771,11 +6783,11 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>95.6861572265625</v>
+        <v>95.68616485595703</v>
       </c>
       <c r="C245" t="n">
         <v>98.11000061035156</v>
@@ -6800,7 +6812,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -6829,7 +6841,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -6858,7 +6870,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -6887,7 +6899,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -6916,32 +6928,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>117.5899963378906</v>
+        <v>118.75</v>
       </c>
       <c r="C250" t="n">
-        <v>117.5899963378906</v>
+        <v>118.75</v>
       </c>
       <c r="D250" t="n">
-        <v>25042700</v>
+        <v>26725900</v>
       </c>
       <c r="E250" t="n">
         <v>11.03</v>
       </c>
       <c r="F250" t="n">
-        <v>10.66092441866642</v>
+        <v>10.766092475068</v>
       </c>
       <c r="G250" t="n">
         <v>345000000</v>
       </c>
       <c r="H250" t="n">
-        <v>40568548736.57227</v>
+        <v>40968750000</v>
       </c>
       <c r="I250" t="n">
-        <v>0.07258753623188406</v>
+        <v>0.0774663768115942</v>
       </c>
     </row>
   </sheetData>
@@ -6973,75 +6985,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7077,13 +7089,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7119,13 +7131,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7161,13 +7173,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7203,13 +7215,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7245,13 +7257,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7278,7 +7290,7 @@
       <c r="I7" t="n">
         <v>7.39</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K7" t="n">
@@ -7291,13 +7303,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7324,7 +7336,7 @@
       <c r="I8" t="n">
         <v>8.529999999999999</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K8" t="n">
@@ -7337,13 +7349,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7370,7 +7382,7 @@
       <c r="I9" t="n">
         <v>8.98</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K9" t="n">
@@ -7383,13 +7395,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40351</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7416,7 +7428,7 @@
       <c r="I10" t="n">
         <v>9.09</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K10" t="n">
@@ -7429,13 +7441,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7462,7 +7474,7 @@
       <c r="I11" t="n">
         <v>5.76</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K11" t="n">
@@ -7475,13 +7487,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7508,7 +7520,7 @@
       <c r="I12" t="n">
         <v>5.809999999999999</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K12" t="n">
@@ -7521,13 +7533,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7554,7 +7566,7 @@
       <c r="I13" t="n">
         <v>5.789999999999999</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K13" t="n">
@@ -7567,13 +7579,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40726</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7600,7 +7612,7 @@
       <c r="I14" t="n">
         <v>6.389999999999999</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K14" t="n">
@@ -7613,13 +7625,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7646,7 +7658,7 @@
       <c r="I15" t="n">
         <v>7.199999999999998</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K15" t="n">
@@ -7659,13 +7671,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7692,7 +7704,7 @@
       <c r="I16" t="n">
         <v>3.909999999999998</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="K16" t="n">
@@ -7705,13 +7717,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7738,7 +7750,7 @@
       <c r="I17" t="n">
         <v>6.919999999999999</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K17" t="n">
@@ -7751,13 +7763,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7784,7 +7796,7 @@
       <c r="I18" t="n">
         <v>2.52</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K18" t="n">
@@ -7797,13 +7809,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7830,7 +7842,7 @@
       <c r="I19" t="n">
         <v>0.7799999999999994</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K19" t="n">
@@ -7843,13 +7855,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -7876,7 +7888,7 @@
       <c r="I20" t="n">
         <v>1.319999999999999</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="K20" t="n">
@@ -7889,13 +7901,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -7922,7 +7934,7 @@
       <c r="I21" t="n">
         <v>-4.490000000000001</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="K21" t="n">
@@ -7935,13 +7947,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -7968,7 +7980,7 @@
       <c r="I22" t="n">
         <v>-1.110000000000001</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="K22" t="n">
@@ -7981,13 +7993,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8014,7 +8026,7 @@
       <c r="I23" t="n">
         <v>-1.570000000000001</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="K23" t="n">
@@ -8027,13 +8039,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8060,7 +8072,7 @@
       <c r="I24" t="n">
         <v>2.569999999999999</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="K24" t="n">
@@ -8073,13 +8085,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8106,7 +8118,7 @@
       <c r="I25" t="n">
         <v>5.909999999999999</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="K25" t="n">
@@ -8119,13 +8131,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8152,7 +8164,7 @@
       <c r="I26" t="n">
         <v>4.859999999999999</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="K26" t="n">
@@ -8165,13 +8177,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8198,7 +8210,7 @@
       <c r="I27" t="n">
         <v>3.109999999999999</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="K27" t="n">
@@ -8211,13 +8223,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8244,7 +8256,7 @@
       <c r="I28" t="n">
         <v>4.889999999999999</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="K28" t="n">
@@ -8257,13 +8269,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8290,7 +8302,7 @@
       <c r="I29" t="n">
         <v>5.699999999999999</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="K29" t="n">
@@ -8303,13 +8315,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8336,7 +8348,7 @@
       <c r="I30" t="n">
         <v>7.869999999999999</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="K30" t="n">
@@ -8349,13 +8361,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8382,7 +8394,7 @@
       <c r="I31" t="n">
         <v>12.16</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="K31" t="n">
@@ -8395,13 +8407,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8428,7 +8440,7 @@
       <c r="I32" t="n">
         <v>10.72</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="K32" t="n">
@@ -8441,13 +8453,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8474,7 +8486,7 @@
       <c r="I33" t="n">
         <v>9.73</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="K33" t="n">
@@ -8487,13 +8499,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8520,7 +8532,7 @@
       <c r="I34" t="n">
         <v>10.64</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="K34" t="n">
@@ -8533,13 +8545,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8566,7 +8578,7 @@
       <c r="I35" t="n">
         <v>9.69</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="K35" t="n">
@@ -8579,13 +8591,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8612,7 +8624,7 @@
       <c r="I36" t="n">
         <v>9.85</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="K36" t="n">
@@ -8625,13 +8637,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8658,7 +8670,7 @@
       <c r="I37" t="n">
         <v>8.93</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="K37" t="n">
@@ -8671,13 +8683,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8704,7 +8716,7 @@
       <c r="I38" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="K38" t="n">
@@ -8717,13 +8729,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8750,7 +8762,7 @@
       <c r="I39" t="n">
         <v>17.91</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="K39" t="n">
@@ -8763,13 +8775,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8796,7 +8808,7 @@
       <c r="I40" t="n">
         <v>17.96</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="K40" t="n">
@@ -8809,13 +8821,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8842,7 +8854,7 @@
       <c r="I41" t="n">
         <v>17.3</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="K41" t="n">
@@ -8855,13 +8867,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43412</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -8888,7 +8900,7 @@
       <c r="I42" t="n">
         <v>16.11</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43412</v>
       </c>
       <c r="K42" t="n">
@@ -8901,13 +8913,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -8934,7 +8946,7 @@
       <c r="I43" t="n">
         <v>9.49</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="K43" t="n">
@@ -8947,13 +8959,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -8980,7 +8992,7 @@
       <c r="I44" t="n">
         <v>8.57</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="K44" t="n">
@@ -8993,13 +9005,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43679</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9026,7 +9038,7 @@
       <c r="I45" t="n">
         <v>9.82</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43679</v>
       </c>
       <c r="K45" t="n">
@@ -9039,13 +9051,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9072,7 +9084,7 @@
       <c r="I46" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="K46" t="n">
@@ -9085,13 +9097,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9118,7 +9130,7 @@
       <c r="I47" t="n">
         <v>10.13</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="K47" t="n">
@@ -9131,13 +9143,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9164,7 +9176,7 @@
       <c r="I48" t="n">
         <v>7.21</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="K48" t="n">
@@ -9177,13 +9189,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9210,7 +9222,7 @@
       <c r="I49" t="n">
         <v>-0.6200000000000001</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="K49" t="n">
@@ -9223,13 +9235,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9256,7 +9268,7 @@
       <c r="I50" t="n">
         <v>-0.3600000000000003</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="K50" t="n">
@@ -9269,13 +9281,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9302,7 +9314,7 @@
       <c r="I51" t="n">
         <v>-1.09</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="K51" t="n">
@@ -9315,13 +9327,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9348,7 +9360,7 @@
       <c r="I52" t="n">
         <v>6.590000000000001</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="K52" t="n">
@@ -9361,13 +9373,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9394,7 +9406,7 @@
       <c r="I53" t="n">
         <v>18.11</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="K53" t="n">
@@ -9407,13 +9419,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9440,7 +9452,7 @@
       <c r="I54" t="n">
         <v>18.31</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="K54" t="n">
@@ -9453,13 +9465,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9486,7 +9498,7 @@
       <c r="I55" t="n">
         <v>19.51</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="K55" t="n">
@@ -9499,13 +9511,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9532,7 +9544,7 @@
       <c r="I56" t="n">
         <v>12.43</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="K56" t="n">
@@ -9545,13 +9557,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9578,7 +9590,7 @@
       <c r="I57" t="n">
         <v>5.5</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="K57" t="n">
@@ -9591,13 +9603,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9624,7 +9636,7 @@
       <c r="I58" t="n">
         <v>0.8200000000000003</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="K58" t="n">
@@ -9637,13 +9649,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44973</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9670,7 +9682,7 @@
       <c r="I59" t="n">
         <v>-3.93</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44973</v>
       </c>
       <c r="K59" t="n">
@@ -9683,13 +9695,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9716,7 +9728,7 @@
       <c r="I60" t="n">
         <v>0.1000000000000001</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="K60" t="n">
@@ -9729,13 +9741,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9762,7 +9774,7 @@
       <c r="I61" t="n">
         <v>3.01</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="K61" t="n">
@@ -9775,13 +9787,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9808,7 +9820,7 @@
       <c r="I62" t="n">
         <v>1.56</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="K62" t="n">
@@ -9821,13 +9833,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -9854,7 +9866,7 @@
       <c r="I63" t="n">
         <v>6.69</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="K63" t="n">
@@ -9867,13 +9879,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -9900,7 +9912,7 @@
       <c r="I64" t="n">
         <v>5.880000000000001</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K64" t="n">
@@ -9913,13 +9925,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -9946,7 +9958,7 @@
       <c r="I65" t="n">
         <v>7.78</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="K65" t="n">
@@ -9959,13 +9971,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -9992,7 +10004,7 @@
       <c r="I66" t="n">
         <v>11.25</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="K66" t="n">
@@ -10005,13 +10017,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10038,7 +10050,7 @@
       <c r="I67" t="n">
         <v>7.5</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="K67" t="n">
@@ -10051,13 +10063,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10084,7 +10096,7 @@
       <c r="I68" t="n">
         <v>6.34</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="K68" t="n">
@@ -10097,13 +10109,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10130,7 +10142,7 @@
       <c r="I69" t="n">
         <v>4.54</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="K69" t="n">
@@ -10143,13 +10155,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10176,7 +10188,7 @@
       <c r="I70" t="n">
         <v>7.31</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="K70" t="n">
@@ -10189,13 +10201,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10222,7 +10234,7 @@
       <c r="I71" t="n">
         <v>9.990000000000002</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="K71" t="n">
@@ -10235,13 +10247,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10268,7 +10280,7 @@
       <c r="I72" t="n">
         <v>9.710000000000003</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="K72" t="n">
@@ -10281,13 +10293,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10314,7 +10326,7 @@
       <c r="I73" t="n">
         <v>11.03</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="K73" t="n">
@@ -10351,52 +10363,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="C2" t="n">
@@ -10425,10 +10437,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40117</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="C3" t="n">
@@ -10457,10 +10469,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C4" t="n">
@@ -10489,10 +10501,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="C5" t="n">
@@ -10521,10 +10533,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="C6" t="n">
@@ -10553,10 +10565,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="C7" t="n">
@@ -10585,10 +10597,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="C8" t="n">
@@ -10617,10 +10629,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="C9" t="n">
@@ -10649,10 +10661,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="C10" t="n">
@@ -10681,10 +10693,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41858</v>
       </c>
       <c r="C11" t="n">
@@ -10713,10 +10725,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="C12" t="n">
@@ -10745,10 +10757,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="C13" t="n">
@@ -10777,10 +10789,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="C14" t="n">
@@ -10809,10 +10821,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="C15" t="n">
@@ -10841,10 +10853,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="C16" t="n">
@@ -10873,10 +10885,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42308</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="C17" t="n">
@@ -10905,10 +10917,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="C18" t="n">
@@ -10937,10 +10949,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="C19" t="n">
@@ -10969,10 +10981,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="C20" t="n">
@@ -11001,10 +11013,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="C21" t="n">
@@ -11033,10 +11045,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="C22" t="n">
@@ -11065,10 +11077,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="C23" t="n">
@@ -11097,10 +11109,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="C24" t="n">
@@ -11129,10 +11141,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="C25" t="n">
@@ -11161,10 +11173,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="C26" t="n">
@@ -11193,10 +11205,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43039</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="C27" t="n">
@@ -11225,10 +11237,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="C28" t="n">
@@ -11257,10 +11269,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="C29" t="n">
@@ -11289,10 +11301,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="C30" t="n">
@@ -11321,10 +11333,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43312</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="C31" t="n">
@@ -11353,10 +11365,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43404</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43412</v>
       </c>
       <c r="C32" t="n">
@@ -11385,10 +11397,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="C33" t="n">
@@ -11417,10 +11429,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43585</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="C34" t="n">
@@ -11449,10 +11461,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43679</v>
       </c>
       <c r="C35" t="n">
@@ -11481,10 +11493,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43769</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="C36" t="n">
@@ -11513,10 +11525,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="C37" t="n">
@@ -11545,10 +11557,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="C38" t="n">
@@ -11577,10 +11589,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="C39" t="n">
@@ -11609,10 +11621,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44135</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="C40" t="n">
@@ -11641,10 +11653,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="C41" t="n">
@@ -11673,10 +11685,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="C42" t="n">
@@ -11705,10 +11717,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44408</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="C43" t="n">
@@ -11737,10 +11749,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44500</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="C44" t="n">
@@ -11769,10 +11781,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="C45" t="n">
@@ -11801,10 +11813,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44681</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="C46" t="n">
@@ -11833,10 +11845,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="C47" t="n">
@@ -11865,10 +11877,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="C48" t="n">
@@ -11897,10 +11909,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44973</v>
       </c>
       <c r="C49" t="n">
@@ -11929,10 +11941,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45046</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="C50" t="n">
@@ -11961,10 +11973,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="C51" t="n">
@@ -11993,10 +12005,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45230</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="C52" t="n">
@@ -12025,10 +12037,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="C53" t="n">
@@ -12057,10 +12069,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45412</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C54" t="n">
@@ -12089,10 +12101,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="C55" t="n">
@@ -12121,10 +12133,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45593</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="C56" t="n">
@@ -12153,10 +12165,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="C57" t="n">
@@ -12185,10 +12197,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45775</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="C58" t="n">
@@ -12217,10 +12229,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45866</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="C59" t="n">
@@ -12249,10 +12261,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45957</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="C60" t="n">
@@ -12281,10 +12293,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="C61" t="n">
@@ -12313,10 +12325,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="C62" t="n">
@@ -12345,10 +12357,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="C63" t="n">
@@ -12395,12 +12407,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/PRU.xlsx
+++ b/salidas/empresas/PRU.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>36.64837265014648</v>
+        <v>36.64836502075195</v>
       </c>
       <c r="C2" t="n">
         <v>75.33999633789062</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>37.47530364990234</v>
+        <v>37.47531890869141</v>
       </c>
       <c r="C3" t="n">
         <v>77.04000091552734</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>36.87701034545898</v>
+        <v>36.87699127197266</v>
       </c>
       <c r="C4" t="n">
         <v>75.80999755859375</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>38.00553894042969</v>
+        <v>38.00553512573242</v>
       </c>
       <c r="C5" t="n">
         <v>78.12999725341797</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>37.04239273071289</v>
+        <v>37.04239654541016</v>
       </c>
       <c r="C6" t="n">
         <v>76.15000152587891</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>37.79635620117188</v>
+        <v>37.7963752746582</v>
       </c>
       <c r="C7" t="n">
         <v>77.69999694824219</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>38.25362396240234</v>
+        <v>38.25363159179688</v>
       </c>
       <c r="C8" t="n">
         <v>78.63999938964844</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>35.70955276489258</v>
+        <v>35.70953369140625</v>
       </c>
       <c r="C9" t="n">
         <v>73.41000366210938</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>37.09103393554688</v>
+        <v>37.09104156494141</v>
       </c>
       <c r="C10" t="n">
         <v>76.25</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>37.42182159423828</v>
+        <v>37.42180633544922</v>
       </c>
       <c r="C11" t="n">
         <v>76.93000030517578</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>40.10713195800781</v>
+        <v>40.10712814331055</v>
       </c>
       <c r="C12" t="n">
         <v>81.48000335693359</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>42.26313400268555</v>
+        <v>42.26311111450195</v>
       </c>
       <c r="C13" t="n">
         <v>85.86000061035156</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>44.763671875</v>
+        <v>44.7636604309082</v>
       </c>
       <c r="C15" t="n">
         <v>90.94000244140625</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>44.42894744873047</v>
+        <v>44.42895126342773</v>
       </c>
       <c r="C16" t="n">
         <v>90.26000213623047</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>46.76213455200195</v>
+        <v>46.76212692260742</v>
       </c>
       <c r="C17" t="n">
         <v>95</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>50.21760559082031</v>
+        <v>50.21759414672852</v>
       </c>
       <c r="C18" t="n">
         <v>102.0199966430664</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>47.85981369018555</v>
+        <v>47.85980606079102</v>
       </c>
       <c r="C19" t="n">
         <v>97.23000335693359</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>43.62660980224609</v>
+        <v>43.62660217285156</v>
       </c>
       <c r="C20" t="n">
         <v>88.62999725341797</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>44.19267654418945</v>
+        <v>44.19266510009766</v>
       </c>
       <c r="C21" t="n">
         <v>89.77999877929688</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>48.03208923339844</v>
+        <v>48.03207778930664</v>
       </c>
       <c r="C22" t="n">
         <v>97.58000183105469</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>47.60878753662109</v>
+        <v>47.60876083374023</v>
       </c>
       <c r="C23" t="n">
         <v>96.72000122070312</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>46.35703277587891</v>
+        <v>46.35703659057617</v>
       </c>
       <c r="C25" t="n">
         <v>93.04000091552734</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>41.88776779174805</v>
+        <v>41.88774871826172</v>
       </c>
       <c r="C26" t="n">
         <v>84.06999969482422</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>36.35719680786133</v>
+        <v>36.3571891784668</v>
       </c>
       <c r="C27" t="n">
         <v>72.97000122070312</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>38.98794555664062</v>
+        <v>38.98793029785156</v>
       </c>
       <c r="C28" t="n">
         <v>78.25</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>37.21916961669922</v>
+        <v>37.21916198730469</v>
       </c>
       <c r="C30" t="n">
         <v>74.69999694824219</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>29.76537895202637</v>
+        <v>29.7653636932373</v>
       </c>
       <c r="C31" t="n">
         <v>59.7400016784668</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>34.36419677734375</v>
+        <v>34.36420059204102</v>
       </c>
       <c r="C32" t="n">
         <v>68.97000122070312</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>36.72590255737305</v>
+        <v>36.72588729858398</v>
       </c>
       <c r="C33" t="n">
         <v>73.70999908447266</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>35.87389755249023</v>
+        <v>35.87388229370117</v>
       </c>
       <c r="C34" t="n">
         <v>72</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>14.9474515914917</v>
+        <v>14.94745826721191</v>
       </c>
       <c r="C35" t="n">
         <v>30</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>11.1936674118042</v>
+        <v>11.19366836547852</v>
       </c>
       <c r="C36" t="n">
         <v>21.70000076293945</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>15.60923957824707</v>
+        <v>15.60923671722412</v>
       </c>
       <c r="C37" t="n">
         <v>30.26000022888184</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>13.28280925750732</v>
+        <v>13.28281784057617</v>
       </c>
       <c r="C38" t="n">
         <v>25.75</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>9.811227798461914</v>
+        <v>9.811223983764648</v>
       </c>
       <c r="C40" t="n">
         <v>19.02000045776367</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>14.89738464355469</v>
+        <v>14.89737701416016</v>
       </c>
       <c r="C41" t="n">
         <v>28.8799991607666</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>20.58706855773926</v>
+        <v>20.58707046508789</v>
       </c>
       <c r="C42" t="n">
         <v>39.90999984741211</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>19.19947242736816</v>
+        <v>19.19946479797363</v>
       </c>
       <c r="C43" t="n">
         <v>37.22000122070312</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>22.83612251281738</v>
+        <v>22.83612060546875</v>
       </c>
       <c r="C44" t="n">
         <v>44.27000045776367</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>26.09104919433594</v>
+        <v>26.09106063842773</v>
       </c>
       <c r="C45" t="n">
         <v>50.58000183105469</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>25.74543571472168</v>
+        <v>25.74544525146484</v>
       </c>
       <c r="C46" t="n">
         <v>49.90999984741211</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>26.0897159576416</v>
+        <v>26.08972549438477</v>
       </c>
       <c r="C48" t="n">
         <v>49.84999847412109</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>26.04262542724609</v>
+        <v>26.04262924194336</v>
       </c>
       <c r="C49" t="n">
         <v>49.7599983215332</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>26.16300773620605</v>
+        <v>26.16300010681152</v>
       </c>
       <c r="C50" t="n">
         <v>49.9900016784668</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>27.42953872680664</v>
+        <v>27.42954635620117</v>
       </c>
       <c r="C51" t="n">
         <v>52.40999984741211</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>31.66356658935547</v>
+        <v>31.66357040405273</v>
       </c>
       <c r="C52" t="n">
         <v>60.5</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>33.26506423950195</v>
+        <v>33.26506805419922</v>
       </c>
       <c r="C53" t="n">
         <v>63.56000137329102</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>30.20337867736816</v>
+        <v>30.20336723327637</v>
       </c>
       <c r="C54" t="n">
         <v>57.70999908447266</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>28.08374786376953</v>
+        <v>28.08374214172363</v>
       </c>
       <c r="C55" t="n">
         <v>53.65999984741211</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>29.98356628417969</v>
+        <v>29.98355865478516</v>
       </c>
       <c r="C56" t="n">
         <v>57.29000091552734</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>26.48226356506348</v>
+        <v>26.48224830627441</v>
       </c>
       <c r="C57" t="n">
         <v>50.59999847412109</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>28.35589981079102</v>
+        <v>28.35589408874512</v>
       </c>
       <c r="C58" t="n">
         <v>54.18000030517578</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>27.51851654052734</v>
+        <v>27.51851463317871</v>
       </c>
       <c r="C59" t="n">
         <v>52.58000183105469</v>
@@ -1684,7 +1684,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>27.09619522094727</v>
+        <v>27.09619331359863</v>
       </c>
       <c r="C60" t="n">
         <v>50.68000030517578</v>
@@ -1703,7 +1703,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>31.38945770263672</v>
+        <v>31.38946151733398</v>
       </c>
       <c r="C61" t="n">
         <v>58.70999908447266</v>
@@ -1741,7 +1741,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>35.1961784362793</v>
+        <v>35.19618225097656</v>
       </c>
       <c r="C63" t="n">
         <v>65.83000183105469</v>
@@ -1764,7 +1764,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>32.92390060424805</v>
+        <v>32.92391204833984</v>
       </c>
       <c r="C64" t="n">
         <v>61.58000183105469</v>
@@ -1787,7 +1787,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>33.90766906738281</v>
+        <v>33.90765762329102</v>
       </c>
       <c r="C65" t="n">
         <v>63.41999816894531</v>
@@ -1810,7 +1810,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>34.10013961791992</v>
+        <v>34.10015106201172</v>
       </c>
       <c r="C66" t="n">
         <v>63.77999877929688</v>
@@ -1833,7 +1833,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>33.9985466003418</v>
+        <v>33.99855422973633</v>
       </c>
       <c r="C67" t="n">
         <v>63.59000015258789</v>
@@ -1856,7 +1856,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>31.3734188079834</v>
+        <v>31.37341499328613</v>
       </c>
       <c r="C68" t="n">
         <v>58.68000030517578</v>
@@ -1879,7 +1879,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>26.84491157531738</v>
+        <v>26.84490013122559</v>
       </c>
       <c r="C69" t="n">
         <v>50.20999908447266</v>
@@ -1902,7 +1902,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>25.05383110046387</v>
+        <v>25.0538215637207</v>
       </c>
       <c r="C70" t="n">
         <v>46.86000061035156</v>
@@ -1925,7 +1925,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>28.97816848754883</v>
+        <v>28.97816467285156</v>
       </c>
       <c r="C71" t="n">
         <v>54.20000076293945</v>
@@ -1944,7 +1944,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>27.8753490447998</v>
+        <v>27.87534713745117</v>
       </c>
       <c r="C72" t="n">
         <v>50.63999938964844</v>
@@ -1963,7 +1963,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>27.58909797668457</v>
+        <v>27.5890998840332</v>
       </c>
       <c r="C73" t="n">
         <v>50.11999893188477</v>
@@ -1982,7 +1982,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>31.50839233398438</v>
+        <v>31.50838851928711</v>
       </c>
       <c r="C74" t="n">
         <v>57.2400016784668</v>
@@ -2001,7 +2001,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>33.66619491577148</v>
+        <v>33.66618347167969</v>
       </c>
       <c r="C75" t="n">
         <v>61.15999984741211</v>
@@ -2024,7 +2024,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>34.89371109008789</v>
+        <v>34.89372253417969</v>
       </c>
       <c r="C76" t="n">
         <v>63.38999938964844</v>
@@ -2047,7 +2047,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>33.32491302490234</v>
+        <v>33.32490921020508</v>
       </c>
       <c r="C77" t="n">
         <v>60.54000091552734</v>
@@ -2093,7 +2093,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>26.65882873535156</v>
+        <v>26.65882682800293</v>
       </c>
       <c r="C79" t="n">
         <v>48.43000030517578</v>
@@ -2116,7 +2116,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>26.57625198364258</v>
+        <v>26.57626152038574</v>
       </c>
       <c r="C80" t="n">
         <v>48.27999877929688</v>
@@ -2139,7 +2139,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>30.00562477111816</v>
+        <v>30.0056266784668</v>
       </c>
       <c r="C81" t="n">
         <v>54.5099983215332</v>
@@ -2162,7 +2162,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>30.00562477111816</v>
+        <v>30.0056266784668</v>
       </c>
       <c r="C82" t="n">
         <v>54.5099983215332</v>
@@ -2185,7 +2185,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>31.40380477905273</v>
+        <v>31.40381050109863</v>
       </c>
       <c r="C83" t="n">
         <v>57.04999923706055</v>
@@ -2208,7 +2208,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>29.63028907775879</v>
+        <v>29.63030242919922</v>
       </c>
       <c r="C84" t="n">
         <v>52.11999893188477</v>
@@ -2231,7 +2231,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>30.31818962097168</v>
+        <v>30.31819343566895</v>
       </c>
       <c r="C85" t="n">
         <v>53.33000183105469</v>
@@ -2250,7 +2250,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>32.90487289428711</v>
+        <v>32.90486526489258</v>
       </c>
       <c r="C86" t="n">
         <v>57.88000106811523</v>
@@ -2269,7 +2269,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>31.82259750366211</v>
+        <v>31.82259941101074</v>
       </c>
       <c r="C87" t="n">
         <v>55.56999969482422</v>
@@ -2315,7 +2315,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>34.59999847412109</v>
+        <v>34.5999870300293</v>
       </c>
       <c r="C89" t="n">
         <v>60.41999816894531</v>
@@ -2367,7 +2367,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>42.07242965698242</v>
+        <v>42.07243347167969</v>
       </c>
       <c r="C91" t="n">
         <v>73.02999877929688</v>
@@ -2396,7 +2396,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>45.49445343017578</v>
+        <v>45.49444961547852</v>
       </c>
       <c r="C92" t="n">
         <v>78.97000122070312</v>
@@ -2425,7 +2425,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>43.35632705688477</v>
+        <v>43.3563232421875</v>
       </c>
       <c r="C93" t="n">
         <v>74.87999725341797</v>
@@ -2454,7 +2454,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>45.15127563476562</v>
+        <v>45.15126419067383</v>
       </c>
       <c r="C94" t="n">
         <v>77.98000335693359</v>
@@ -2483,7 +2483,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>47.12568283081055</v>
+        <v>47.12569427490234</v>
       </c>
       <c r="C95" t="n">
         <v>81.38999938964844</v>
@@ -2512,7 +2512,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>51.6967658996582</v>
+        <v>51.69676208496094</v>
       </c>
       <c r="C96" t="n">
         <v>88.76000213623047</v>
@@ -2541,7 +2541,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>53.71198272705078</v>
+        <v>53.71197128295898</v>
       </c>
       <c r="C97" t="n">
         <v>92.22000122070312</v>
@@ -2566,7 +2566,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>49.15151596069336</v>
+        <v>49.15153503417969</v>
       </c>
       <c r="C98" t="n">
         <v>84.38999938964844</v>
@@ -2645,7 +2645,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>47.28731918334961</v>
+        <v>47.28733062744141</v>
       </c>
       <c r="C101" t="n">
         <v>80.68000030517578</v>
@@ -2672,7 +2672,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>48.47158050537109</v>
+        <v>48.47158813476562</v>
       </c>
       <c r="C102" t="n">
         <v>82.16000366210938</v>
@@ -2701,7 +2701,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>52.37125015258789</v>
+        <v>52.37125396728516</v>
       </c>
       <c r="C103" t="n">
         <v>88.76999664306641</v>
@@ -2730,7 +2730,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>51.30931091308594</v>
+        <v>51.30931854248047</v>
       </c>
       <c r="C104" t="n">
         <v>86.97000122070312</v>
@@ -2759,7 +2759,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>53.23298263549805</v>
+        <v>53.23299407958984</v>
       </c>
       <c r="C105" t="n">
         <v>89.69999694824219</v>
@@ -2788,7 +2788,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>52.18850326538086</v>
+        <v>52.18849945068359</v>
       </c>
       <c r="C106" t="n">
         <v>87.94000244140625</v>
@@ -2817,7 +2817,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>52.54457473754883</v>
+        <v>52.54458999633789</v>
       </c>
       <c r="C107" t="n">
         <v>88.54000091552734</v>
@@ -2846,7 +2846,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>50.78231430053711</v>
+        <v>50.78230667114258</v>
       </c>
       <c r="C108" t="n">
         <v>84.98000335693359</v>
@@ -2875,7 +2875,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>54.0570182800293</v>
+        <v>54.05702209472656</v>
       </c>
       <c r="C109" t="n">
         <v>90.45999908447266</v>
@@ -2900,7 +2900,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>45.34434127807617</v>
+        <v>45.34433746337891</v>
       </c>
       <c r="C110" t="n">
         <v>75.87999725341797</v>
@@ -2925,7 +2925,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>48.66580581665039</v>
+        <v>48.66580200195312</v>
       </c>
       <c r="C111" t="n">
         <v>80.84999847412109</v>
@@ -2954,7 +2954,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>48.34075546264648</v>
+        <v>48.34076690673828</v>
       </c>
       <c r="C112" t="n">
         <v>80.30999755859375</v>
@@ -3012,7 +3012,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>51.27630996704102</v>
+        <v>51.27633666992188</v>
       </c>
       <c r="C114" t="n">
         <v>84.61000061035156</v>
@@ -3041,7 +3041,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>53.03987884521484</v>
+        <v>53.03987121582031</v>
       </c>
       <c r="C115" t="n">
         <v>87.51999664306641</v>
@@ -3070,7 +3070,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>53.5489501953125</v>
+        <v>53.54894638061523</v>
       </c>
       <c r="C116" t="n">
         <v>88.36000061035156</v>
@@ -3099,7 +3099,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>49.2431755065918</v>
+        <v>49.24318695068359</v>
       </c>
       <c r="C117" t="n">
         <v>80.69999694824219</v>
@@ -3128,7 +3128,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>46.50337982177734</v>
+        <v>46.50339508056641</v>
       </c>
       <c r="C118" t="n">
         <v>76.20999908447266</v>
@@ -3157,7 +3157,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>50.3415412902832</v>
+        <v>50.34156036376953</v>
       </c>
       <c r="C119" t="n">
         <v>82.5</v>
@@ -3186,7 +3186,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>53.2392578125</v>
+        <v>53.23928070068359</v>
       </c>
       <c r="C120" t="n">
         <v>86.55000305175781</v>
@@ -3244,7 +3244,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>43.10812377929688</v>
+        <v>43.10811614990234</v>
       </c>
       <c r="C122" t="n">
         <v>70.08000183105469</v>
@@ -3273,7 +3273,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>41.08862686157227</v>
+        <v>41.0886344909668</v>
       </c>
       <c r="C123" t="n">
         <v>66.08999633789062</v>
@@ -3302,7 +3302,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>44.89968872070312</v>
+        <v>44.89969635009766</v>
       </c>
       <c r="C124" t="n">
         <v>72.22000122070312</v>
@@ -3389,7 +3389,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>44.75527572631836</v>
+        <v>44.7552604675293</v>
       </c>
       <c r="C127" t="n">
         <v>71.33999633789062</v>
@@ -3418,7 +3418,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>47.23331832885742</v>
+        <v>47.23332214355469</v>
       </c>
       <c r="C128" t="n">
         <v>75.29000091552734</v>
@@ -3447,7 +3447,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>50.25894165039062</v>
+        <v>50.2589225769043</v>
       </c>
       <c r="C129" t="n">
         <v>79.37999725341797</v>
@@ -3476,7 +3476,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>51.6961669921875</v>
+        <v>51.69618225097656</v>
       </c>
       <c r="C130" t="n">
         <v>81.65000152587891</v>
@@ -3534,7 +3534,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>64.1470947265625</v>
+        <v>64.14707946777344</v>
       </c>
       <c r="C132" t="n">
         <v>100.5999984741211</v>
@@ -3563,7 +3563,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>66.35330963134766</v>
+        <v>66.35337066650391</v>
       </c>
       <c r="C133" t="n">
         <v>104.0599975585938</v>
@@ -3592,7 +3592,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>67.02287292480469</v>
+        <v>67.02286529541016</v>
       </c>
       <c r="C134" t="n">
         <v>105.1100006103516</v>
@@ -3621,7 +3621,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>70.95999145507812</v>
+        <v>70.95999908447266</v>
       </c>
       <c r="C135" t="n">
         <v>110.5400009155273</v>
@@ -3650,7 +3650,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>68.48209381103516</v>
+        <v>68.48211669921875</v>
       </c>
       <c r="C136" t="n">
         <v>106.6800003051758</v>
@@ -3679,7 +3679,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>68.70680236816406</v>
+        <v>68.70677947998047</v>
       </c>
       <c r="C137" t="n">
         <v>107.0299987792969</v>
@@ -3708,7 +3708,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>67.79888916015625</v>
+        <v>67.79890441894531</v>
       </c>
       <c r="C138" t="n">
         <v>104.8499984741211</v>
@@ -3737,7 +3737,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>69.92627716064453</v>
+        <v>69.92630004882812</v>
       </c>
       <c r="C139" t="n">
         <v>108.1399993896484</v>
@@ -3766,7 +3766,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>73.2176513671875</v>
+        <v>73.21761322021484</v>
       </c>
       <c r="C140" t="n">
         <v>113.2300033569336</v>
@@ -3795,7 +3795,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>66.49349212646484</v>
+        <v>66.49352264404297</v>
       </c>
       <c r="C141" t="n">
         <v>102.0800018310547</v>
@@ -3824,7 +3824,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>69.25537872314453</v>
+        <v>69.25538635253906</v>
       </c>
       <c r="C142" t="n">
         <v>106.3199996948242</v>
@@ -3853,7 +3853,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>71.9521484375</v>
+        <v>71.95211791992188</v>
       </c>
       <c r="C143" t="n">
         <v>110.4599990844727</v>
@@ -3882,7 +3882,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>75.97600555419922</v>
+        <v>75.97602081298828</v>
       </c>
       <c r="C144" t="n">
         <v>115.8399963378906</v>
@@ -3911,7 +3911,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>75.41199493408203</v>
+        <v>75.41197967529297</v>
       </c>
       <c r="C145" t="n">
         <v>114.9800033569336</v>
@@ -3940,7 +3940,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>77.93051147460938</v>
+        <v>77.93052673339844</v>
       </c>
       <c r="C146" t="n">
         <v>118.8199996948242</v>
@@ -3969,7 +3969,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>70.31039428710938</v>
+        <v>70.31040191650391</v>
       </c>
       <c r="C147" t="n">
         <v>106.3199996948242</v>
@@ -3998,7 +3998,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>68.47858428955078</v>
+        <v>68.47857666015625</v>
       </c>
       <c r="C148" t="n">
         <v>103.5500030517578</v>
@@ -4027,7 +4027,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>70.31039428710938</v>
+        <v>70.31040191650391</v>
       </c>
       <c r="C149" t="n">
         <v>106.3199996948242</v>
@@ -4056,7 +4056,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>64.60887145996094</v>
+        <v>64.60886383056641</v>
       </c>
       <c r="C150" t="n">
         <v>96.83999633789062</v>
@@ -4114,7 +4114,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>67.32426452636719</v>
+        <v>67.32424163818359</v>
       </c>
       <c r="C152" t="n">
         <v>100.9100036621094</v>
@@ -4143,7 +4143,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>66.15218353271484</v>
+        <v>66.15221405029297</v>
       </c>
       <c r="C153" t="n">
         <v>98.25</v>
@@ -4172,7 +4172,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>68.21925354003906</v>
+        <v>68.21923828125</v>
       </c>
       <c r="C154" t="n">
         <v>101.3199996948242</v>
@@ -4201,7 +4201,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>63.14250564575195</v>
+        <v>63.14250946044922</v>
       </c>
       <c r="C155" t="n">
         <v>93.77999877929688</v>
@@ -4259,7 +4259,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>55.45622634887695</v>
+        <v>55.45621871948242</v>
       </c>
       <c r="C157" t="n">
         <v>81.55000305175781</v>
@@ -4288,7 +4288,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>62.65769577026367</v>
+        <v>62.65771865844727</v>
       </c>
       <c r="C158" t="n">
         <v>92.13999938964844</v>
@@ -4317,7 +4317,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>65.88037109375</v>
+        <v>65.88036346435547</v>
       </c>
       <c r="C159" t="n">
         <v>95.84999847412109</v>
@@ -4346,7 +4346,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>63.15167236328125</v>
+        <v>63.15165710449219</v>
       </c>
       <c r="C160" t="n">
         <v>91.87999725341797</v>
@@ -4375,7 +4375,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>72.65739440917969</v>
+        <v>72.65740966796875</v>
       </c>
       <c r="C161" t="n">
         <v>105.7099990844727</v>
@@ -4462,7 +4462,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>70.357666015625</v>
+        <v>70.35768890380859</v>
       </c>
       <c r="C164" t="n">
         <v>101.3099975585938</v>
@@ -4491,7 +4491,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>56.3072509765625</v>
+        <v>56.3072624206543</v>
       </c>
       <c r="C165" t="n">
         <v>80.08999633789062</v>
@@ -4520,7 +4520,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>63.23933410644531</v>
+        <v>63.23933029174805</v>
       </c>
       <c r="C166" t="n">
         <v>89.94999694824219</v>
@@ -4549,7 +4549,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>64.07595062255859</v>
+        <v>64.07595825195312</v>
       </c>
       <c r="C167" t="n">
         <v>91.13999938964844</v>
@@ -4578,7 +4578,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>66.52017974853516</v>
+        <v>66.52019500732422</v>
       </c>
       <c r="C168" t="n">
         <v>93.62000274658203</v>
@@ -4607,7 +4607,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>66.60544586181641</v>
+        <v>66.60545349121094</v>
       </c>
       <c r="C169" t="n">
         <v>93.73999786376953</v>
@@ -4665,7 +4665,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>54.23398590087891</v>
+        <v>54.2340087890625</v>
       </c>
       <c r="C171" t="n">
         <v>75.44999694824219</v>
@@ -4723,7 +4723,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>44.83200454711914</v>
+        <v>44.83200073242188</v>
       </c>
       <c r="C173" t="n">
         <v>62.36999893188477</v>
@@ -4752,7 +4752,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>44.6705436706543</v>
+        <v>44.67053985595703</v>
       </c>
       <c r="C174" t="n">
         <v>60.95999908447266</v>
@@ -4810,7 +4810,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>46.43654632568359</v>
+        <v>46.43655014038086</v>
       </c>
       <c r="C176" t="n">
         <v>63.36999893188477</v>
@@ -4839,7 +4839,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>50.48459625244141</v>
+        <v>50.4846076965332</v>
       </c>
       <c r="C177" t="n">
         <v>67.76999664306641</v>
@@ -4866,7 +4866,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>47.31860733032227</v>
+        <v>47.31861877441406</v>
       </c>
       <c r="C178" t="n">
         <v>63.52000045776367</v>
@@ -4893,7 +4893,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>47.69108581542969</v>
+        <v>47.69107818603516</v>
       </c>
       <c r="C179" t="n">
         <v>64.01999664306641</v>
@@ -4920,7 +4920,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>57.1635856628418</v>
+        <v>57.16358947753906</v>
       </c>
       <c r="C180" t="n">
         <v>75.62000274658203</v>
@@ -4947,7 +4947,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>59.015625</v>
+        <v>59.01560211181641</v>
       </c>
       <c r="C181" t="n">
         <v>78.06999969482422</v>
@@ -4974,7 +4974,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>59.17435073852539</v>
+        <v>59.17436599731445</v>
       </c>
       <c r="C182" t="n">
         <v>78.27999877929688</v>
@@ -5001,7 +5001,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>66.49467468261719</v>
+        <v>66.49466705322266</v>
       </c>
       <c r="C183" t="n">
         <v>86.72000122070312</v>
@@ -5028,7 +5028,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>69.8531494140625</v>
+        <v>69.85313415527344</v>
       </c>
       <c r="C184" t="n">
         <v>91.09999847412109</v>
@@ -5055,7 +5055,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>76.95347595214844</v>
+        <v>76.95346069335938</v>
       </c>
       <c r="C185" t="n">
         <v>100.3600006103516</v>
@@ -5082,7 +5082,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>82.91381072998047</v>
+        <v>82.91382598876953</v>
       </c>
       <c r="C186" t="n">
         <v>106.9700012207031</v>
@@ -5111,7 +5111,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>79.42581939697266</v>
+        <v>79.42581176757812</v>
       </c>
       <c r="C187" t="n">
         <v>102.4700012207031</v>
@@ -5140,7 +5140,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>77.72831726074219</v>
+        <v>77.72830963134766</v>
       </c>
       <c r="C188" t="n">
         <v>100.2799987792969</v>
@@ -5169,7 +5169,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>82.98356628417969</v>
+        <v>82.98354339599609</v>
       </c>
       <c r="C189" t="n">
         <v>105.879997253418</v>
@@ -5198,7 +5198,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>82.45059204101562</v>
+        <v>82.45059967041016</v>
       </c>
       <c r="C190" t="n">
         <v>105.1999969482422</v>
@@ -5227,7 +5227,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>86.25180053710938</v>
+        <v>86.25179290771484</v>
       </c>
       <c r="C191" t="n">
         <v>110.0500030517578</v>
@@ -5256,7 +5256,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>81.02101135253906</v>
+        <v>81.02099609375</v>
       </c>
       <c r="C192" t="n">
         <v>102.2600021362305</v>
@@ -5314,7 +5314,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>88.3973388671875</v>
+        <v>88.39736938476562</v>
       </c>
       <c r="C194" t="n">
         <v>111.5699996948242</v>
@@ -5343,7 +5343,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>89.36333465576172</v>
+        <v>89.36334228515625</v>
       </c>
       <c r="C195" t="n">
         <v>111.6600036621094</v>
@@ -5401,7 +5401,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>86.84233093261719</v>
+        <v>86.84234619140625</v>
       </c>
       <c r="C197" t="n">
         <v>108.5100021362305</v>
@@ -5430,7 +5430,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>86.08017730712891</v>
+        <v>86.0802001953125</v>
       </c>
       <c r="C198" t="n">
         <v>106.25</v>
@@ -5517,7 +5517,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>78.48427581787109</v>
+        <v>78.48426818847656</v>
       </c>
       <c r="C201" t="n">
         <v>95.75</v>
@@ -5546,7 +5546,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>70.31209564208984</v>
+        <v>70.31208801269531</v>
       </c>
       <c r="C202" t="n">
         <v>85.77999877929688</v>
@@ -5575,7 +5575,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>86.22206878662109</v>
+        <v>86.22205352783203</v>
       </c>
       <c r="C203" t="n">
         <v>105.1900024414062</v>
@@ -5633,7 +5633,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>82.44709777832031</v>
+        <v>82.44709014892578</v>
       </c>
       <c r="C205" t="n">
         <v>99.45999908447266</v>
@@ -5662,7 +5662,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>86.98972320556641</v>
+        <v>86.98971557617188</v>
       </c>
       <c r="C206" t="n">
         <v>104.9400024414062</v>
@@ -5691,7 +5691,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>83.91197967529297</v>
+        <v>83.9119873046875</v>
       </c>
       <c r="C207" t="n">
         <v>100</v>
@@ -5718,7 +5718,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>69.42877197265625</v>
+        <v>69.42879486083984</v>
       </c>
       <c r="C208" t="n">
         <v>82.73999786376953</v>
@@ -5745,7 +5745,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>73.00342559814453</v>
+        <v>73.00344085693359</v>
       </c>
       <c r="C209" t="n">
         <v>87</v>
@@ -5772,7 +5772,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>67.05197906494141</v>
+        <v>67.05199432373047</v>
       </c>
       <c r="C210" t="n">
         <v>78.69000244140625</v>
@@ -5830,7 +5830,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>82.21941375732422</v>
+        <v>82.21940612792969</v>
       </c>
       <c r="C212" t="n">
         <v>96.48999786376953</v>
@@ -5888,7 +5888,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>81.96002960205078</v>
+        <v>81.96003723144531</v>
       </c>
       <c r="C214" t="n">
         <v>94.88999938964844</v>
@@ -5917,7 +5917,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>78.98013305664062</v>
+        <v>78.98014831542969</v>
       </c>
       <c r="C215" t="n">
         <v>91.44000244140625</v>
@@ -5946,7 +5946,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>85.57337951660156</v>
+        <v>85.57338714599609</v>
       </c>
       <c r="C216" t="n">
         <v>97.77999877929688</v>
@@ -6033,7 +6033,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>96.53219604492188</v>
+        <v>96.53220367431641</v>
       </c>
       <c r="C219" t="n">
         <v>108.9899978637695</v>
@@ -6062,7 +6062,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>103.9809265136719</v>
+        <v>103.9809188842773</v>
       </c>
       <c r="C220" t="n">
         <v>117.4000015258789</v>
@@ -6091,7 +6091,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>97.85189819335938</v>
+        <v>97.85189056396484</v>
       </c>
       <c r="C221" t="n">
         <v>110.4800033569336</v>
@@ -6120,7 +6120,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>107.7483901977539</v>
+        <v>107.7483978271484</v>
       </c>
       <c r="C222" t="n">
         <v>120.3499984741211</v>
@@ -6149,7 +6149,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>104.9192886352539</v>
+        <v>104.9192657470703</v>
       </c>
       <c r="C223" t="n">
         <v>117.1900024414062</v>
@@ -6178,7 +6178,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>112.1980056762695</v>
+        <v>112.1979827880859</v>
       </c>
       <c r="C224" t="n">
         <v>125.3199996948242</v>
@@ -6207,7 +6207,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>109.7054824829102</v>
+        <v>109.7054901123047</v>
       </c>
       <c r="C225" t="n">
         <v>121.1600036621094</v>
@@ -6265,7 +6265,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>110.9006881713867</v>
+        <v>110.9006958007812</v>
       </c>
       <c r="C227" t="n">
         <v>122.4800033569336</v>
@@ -6294,7 +6294,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>118.3764801025391</v>
+        <v>118.3764724731445</v>
       </c>
       <c r="C228" t="n">
         <v>129.4100036621094</v>
@@ -6323,7 +6323,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>108.4241027832031</v>
+        <v>108.4241104125977</v>
       </c>
       <c r="C229" t="n">
         <v>118.5299987792969</v>
@@ -6410,7 +6410,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>103.4095001220703</v>
+        <v>103.4095153808594</v>
       </c>
       <c r="C232" t="n">
         <v>111.6800003051758</v>
@@ -6468,7 +6468,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>97.41429901123047</v>
+        <v>97.41429138183594</v>
       </c>
       <c r="C234" t="n">
         <v>103.8899993896484</v>
@@ -6555,7 +6555,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>104.1432800292969</v>
+        <v>104.1432876586914</v>
       </c>
       <c r="C237" t="n">
         <v>109.6600036621094</v>
@@ -6584,7 +6584,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>98.52110290527344</v>
+        <v>98.52109527587891</v>
       </c>
       <c r="C238" t="n">
         <v>103.7399978637695</v>
@@ -6613,7 +6613,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>98.76802062988281</v>
+        <v>98.76801300048828</v>
       </c>
       <c r="C239" t="n">
         <v>104</v>
@@ -6642,7 +6642,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>104.1627197265625</v>
+        <v>104.162727355957</v>
       </c>
       <c r="C240" t="n">
         <v>108.25</v>
@@ -6671,7 +6671,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>108.6178970336914</v>
+        <v>108.6179046630859</v>
       </c>
       <c r="C241" t="n">
         <v>112.879997253418</v>
@@ -6700,7 +6700,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>106.9147415161133</v>
+        <v>106.9147491455078</v>
       </c>
       <c r="C242" t="n">
         <v>111.1100006103516</v>
@@ -6787,7 +6787,7 @@
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>95.68616485595703</v>
+        <v>95.6861572265625</v>
       </c>
       <c r="C245" t="n">
         <v>98.11000061035156</v>
